--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486546_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486546_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1381</v>
+        <v>4.5912</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6342</v>
+        <v>6.8955</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.496</v>
+        <v>-2.3043</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7313</v>
+        <v>0.1507</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6305</v>
+        <v>1.7429</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.3619</v>
+        <v>-1.5921</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7838</v>
+        <v>3.6285</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4253</v>
+        <v>3.4372</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.6415</v>
+        <v>0.1912</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.5151</v>
+        <v>-3.4777</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7948</v>
+        <v>-1.6943</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7204</v>
+        <v>-1.7834</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3926</v>
+        <v>1.5225</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
         <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9257</v>
+        <v>1.336</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9824</v>
+        <v>1.1392</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0567</v>
+        <v>0.1968</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5512</v>
+        <v>1.582</v>
       </c>
       <c r="W2" t="n">
-        <v>2.0854</v>
+        <v>3.2154</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5342</v>
+        <v>-1.6334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6376</v>
+        <v>4.5061</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6653</v>
+        <v>5.0637</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0276</v>
+        <v>-0.5577</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7832</v>
+        <v>-0.7313</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3345</v>
+        <v>1.6305</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4486</v>
+        <v>-2.3619</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1692</v>
+        <v>1.7838</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1309</v>
+        <v>3.4253</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0382</v>
+        <v>-1.6415</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9523</v>
+        <v>-2.5151</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4654</v>
+        <v>-1.7948</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4869</v>
+        <v>-0.7204</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>2.3926</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R3" t="n">
-        <v>0.435</v>
+        <v>2.6101</v>
       </c>
       <c r="S3" t="n">
-        <v>5.2256</v>
+        <v>1.2936</v>
       </c>
       <c r="T3" t="n">
-        <v>5.1709</v>
+        <v>1.412</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0547</v>
+        <v>-0.1184</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7602</v>
+        <v>1.5512</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3252</v>
+        <v>2.0854</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6066</v>
+        <v>2.8013</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4485</v>
+        <v>3.9831</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8419</v>
+        <v>-1.1817</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1507</v>
+        <v>-0.7832</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7429</v>
+        <v>-0.3345</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5921</v>
+        <v>-0.4486</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6285</v>
+        <v>0.1692</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4372</v>
+        <v>0.1309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1912</v>
+        <v>0.0382</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.4777</v>
+        <v>-0.9523</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6943</v>
+        <v>-0.4654</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7834</v>
+        <v>-0.4869</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6101</v>
+        <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3513</v>
+        <v>2.3893</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6922</v>
+        <v>2.4887</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6591</v>
+        <v>-0.0994</v>
       </c>
       <c r="V4" t="n">
-        <v>1.582</v>
+        <v>0.7602</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2154</v>
+        <v>1.3252</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6334</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0718</v>
+        <v>0.1141</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0829</v>
+        <v>1.9711</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0111</v>
+        <v>-1.857</v>
       </c>
       <c r="G5" t="n">
         <v>-0.151</v>
@@ -844,13 +844,13 @@
         <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1268</v>
+        <v>0.1691</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4711</v>
+        <v>0.3593</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3443</v>
+        <v>-0.1902</v>
       </c>
       <c r="V5" t="n">
         <v>-0.339</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9613</v>
+        <v>-0.3447</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3255</v>
+        <v>0.5686</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6358</v>
+        <v>-0.9133</v>
       </c>
       <c r="G6" t="n">
         <v>0.4257</v>
@@ -922,13 +922,13 @@
         <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2571</v>
+        <v>0.3596</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.274</v>
+        <v>0.6201</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0169</v>
+        <v>-0.2605</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7489</v>
+        <v>-0.401</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6687</v>
+        <v>0.398</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0802</v>
+        <v>-0.799</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.7693</v>
+        <v>-3.6703</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.5756</v>
+        <v>-2.7038</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1937</v>
+        <v>-0.9666</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.5675</v>
+        <v>-2.1696</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8607</v>
+        <v>-1.1585</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7068</v>
+        <v>-1.0112</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2018</v>
+        <v>-1.5007</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7149</v>
+        <v>-1.5453</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4869</v>
+        <v>0.0446</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7401</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6443</v>
+        <v>0.6826</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8362</v>
+        <v>1.3952</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1919</v>
+        <v>-0.7126</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1162</v>
+        <v>2.8042</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4552</v>
+        <v>2.2599</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.339</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>Y. JOSEPH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7652</v>
+        <v>-0.5177</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7196</v>
+        <v>0.921</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0456</v>
+        <v>-1.4386</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.6703</v>
+        <v>-1.4036</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7038</v>
+        <v>0.4228</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9666</v>
+        <v>-1.8264</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1696</v>
+        <v>0.2476</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1585</v>
+        <v>1.3536</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.0112</v>
+        <v>-1.106</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5007</v>
+        <v>-1.6512</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5453</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0446</v>
+        <v>-0.7204</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6816</v>
+        <v>0.0159</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2776</v>
+        <v>0.6309</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-0.615</v>
       </c>
       <c r="V8" t="n">
-        <v>2.8042</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2599</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5443</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. JOSEPH</t>
+          <t>J. BONE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1863</v>
+        <v>-1.9881</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5319</v>
+        <v>-0.1937</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6544</v>
+        <v>-1.7944</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4036</v>
+        <v>-1.6697</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4228</v>
+        <v>-2.4968</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8264</v>
+        <v>0.8272</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2476</v>
+        <v>-1.0169</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3536</v>
+        <v>-1.2679</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.106</v>
+        <v>0.251</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6512</v>
+        <v>-0.6528</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-1.2289</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7204</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6527</v>
+        <v>0.758</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.822</v>
+        <v>0.8232</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8307</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.5989</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>-2.5989</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BONE</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9361</v>
+        <v>-2.3269</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8643</v>
+        <v>-1.3392</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0718</v>
+        <v>-0.9877</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6697</v>
+        <v>-3.7693</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4968</v>
+        <v>-2.5756</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8272</v>
+        <v>-1.1937</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0169</v>
+        <v>-2.5675</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2679</v>
+        <v>-1.8607</v>
       </c>
       <c r="L10" t="n">
-        <v>0.251</v>
+        <v>-0.7068</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6528</v>
+        <v>-1.2018</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2289</v>
+        <v>-0.7149</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.4869</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5225</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.19</v>
+        <v>1.0662</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1526</v>
+        <v>1.1657</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3426</v>
+        <v>-0.0994</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.5989</v>
+        <v>2.1162</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5989</v>
+        <v>-0.339</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9177</v>
+        <v>-3.4283</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.755</v>
+        <v>-2.4198</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1627</v>
+        <v>-1.0086</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8803</v>
@@ -1312,13 +1312,13 @@
         <v>2.8276</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1334</v>
+        <v>0.2019</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4488</v>
+        <v>-0.2947</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8902</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9588</v>
+        <v>-5.0262</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1267</v>
+        <v>-2.0091</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8321</v>
+        <v>-3.0171</v>
       </c>
       <c r="G12" t="n">
         <v>-6.4111</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1918</v>
+        <v>0.7409</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6044</v>
+        <v>0.5131</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4127</v>
+        <v>0.2277</v>
       </c>
       <c r="V12" t="n">
         <v>-0.226</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.020199999999999</v>
+        <v>-2.0202</v>
       </c>
       <c r="E13" t="n">
         <v>13.8392</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.8592</v>
+        <v>-15.8594</v>
       </c>
       <c r="G13" t="n">
         <v>-19.8934</v>
@@ -1444,7 +1444,7 @@
         <v>-1.8109</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8504</v>
+        <v>3.850399999999999</v>
       </c>
       <c r="L13" t="n">
         <v>-5.6616</v>
@@ -1459,7 +1459,7 @@
         <v>-6.0364</v>
       </c>
       <c r="P13" t="n">
-        <v>6.524999999999999</v>
+        <v>6.525</v>
       </c>
       <c r="Q13" t="n">
         <v>-8.700199999999999</v>
@@ -1468,16 +1468,16 @@
         <v>15.2254</v>
       </c>
       <c r="S13" t="n">
-        <v>8.718299999999997</v>
+        <v>8.718399999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>10.7492</v>
+        <v>10.7493</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0308</v>
+        <v>-2.0309</v>
       </c>
       <c r="V13" t="n">
-        <v>2.629700000000001</v>
+        <v>2.6297</v>
       </c>
       <c r="W13" t="n">
         <v>13.6011</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.9598</v>
+        <v>10.9997</v>
       </c>
       <c r="E14" t="n">
-        <v>10.6362</v>
+        <v>10.748</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3236</v>
+        <v>0.2517</v>
       </c>
       <c r="G14" t="n">
         <v>7.6983</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8462</v>
+        <v>-0.8063</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0721</v>
+        <v>0.1839</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9184</v>
+        <v>-0.9902</v>
       </c>
       <c r="V14" t="n">
         <v>3.0202</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4658</v>
+        <v>1.7708</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8026</v>
+        <v>3.0203</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3369</v>
+        <v>-1.2495</v>
       </c>
       <c r="G15" t="n">
         <v>1.5532</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5874</v>
+        <v>-0.1076</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0911</v>
+        <v>0.3088</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5038</v>
+        <v>-0.4164</v>
       </c>
       <c r="V15" t="n">
         <v>0.7602</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.144</v>
+        <v>1.7516</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7177</v>
+        <v>2.053</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5737</v>
+        <v>-0.3014</v>
       </c>
       <c r="G16" t="n">
         <v>2.1168</v>
@@ -1702,13 +1702,13 @@
         <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.1923</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.137</v>
+        <v>0.1983</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6629</v>
+        <v>-0.3906</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3904</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9796</v>
+        <v>1.2956</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3324</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6472</v>
+        <v>0.7397</v>
       </c>
       <c r="G17" t="n">
         <v>0.8495</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5224</v>
+        <v>-0.2064</v>
       </c>
       <c r="T17" t="n">
-        <v>0.012</v>
+        <v>0.2355</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5344</v>
+        <v>-0.4419</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. CZERAPOWICZ</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5218</v>
+        <v>1.0439</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4991</v>
+        <v>1.3109</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9774</v>
+        <v>-0.267</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4937</v>
+        <v>-0.015</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1311</v>
+        <v>-0.45</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6248</v>
+        <v>0.4351</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9369</v>
+        <v>0.0291</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4197</v>
+        <v>0.8307</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5172</v>
+        <v>-0.8016</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5568</v>
+        <v>-0.0441</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5508</v>
+        <v>-1.2808</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1076</v>
+        <v>1.2367</v>
       </c>
       <c r="P18" t="n">
         <v>-0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R18" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5055</v>
+        <v>-0.9836</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6498</v>
+        <v>0.3269</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1443</v>
+        <v>-1.3105</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.2599</v>
+        <v>2.2599</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3232</v>
+        <v>0.2202</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5286</v>
+        <v>-0.1187</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2054</v>
+        <v>0.3389</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.015</v>
+        <v>0.1003</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.45</v>
+        <v>-0.0487</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4351</v>
+        <v>0.149</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0291</v>
+        <v>0.0182</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8307</v>
+        <v>0.0182</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8016</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0441</v>
+        <v>0.082</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2808</v>
+        <v>-0.067</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2367</v>
+        <v>0.149</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2175</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7043</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4554</v>
+        <v>-0.137</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2488</v>
+        <v>0.0394</v>
       </c>
       <c r="V19" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1636</v>
+        <v>-0.7335</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1187</v>
+        <v>1.3009</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2824</v>
+        <v>-2.0344</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1003</v>
+        <v>1.0684</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0487</v>
+        <v>-0.079</v>
       </c>
       <c r="I20" t="n">
-        <v>0.149</v>
+        <v>1.1475</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0182</v>
+        <v>2.2911</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0182</v>
+        <v>1.4663</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.8248</v>
       </c>
       <c r="M20" t="n">
-        <v>0.082</v>
+        <v>-1.2226</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.067</v>
+        <v>-1.5453</v>
       </c>
       <c r="O20" t="n">
-        <v>0.149</v>
+        <v>0.3227</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1542</v>
+        <v>0.0012</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.137</v>
+        <v>0.3149</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0172</v>
+        <v>-0.3137</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.1507</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1507</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>C. CZERAPOWICZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1747</v>
+        <v>-1.2163</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8597</v>
+        <v>0.8228</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0344</v>
+        <v>-2.039</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0684</v>
+        <v>1.4937</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.079</v>
+        <v>-0.1311</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1475</v>
+        <v>1.6248</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2911</v>
+        <v>0.9369</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4663</v>
+        <v>0.4197</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8248</v>
+        <v>0.5172</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2226</v>
+        <v>0.5568</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5453</v>
+        <v>-0.5508</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3227</v>
+        <v>1.1076</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.2325</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8736</v>
+        <v>0.9734</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3137</v>
+        <v>-1.2059</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1507</v>
+        <v>-2.2599</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1507</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.149</v>
+        <v>-1.6095</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0358</v>
+        <v>2.4828</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.1847</v>
+        <v>-4.0923</v>
       </c>
       <c r="G22" t="n">
         <v>3.8755</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0245</v>
+        <v>-1.485</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.536</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4886</v>
+        <v>-1.3961</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2599</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8202</v>
+        <v>-2.2563</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5217</v>
+        <v>-1.4099</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2986</v>
+        <v>-0.8464</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3281</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2948</v>
+        <v>-0.7309</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.399</v>
+        <v>-0.2872</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8959</v>
+        <v>-0.4437</v>
       </c>
       <c r="V23" t="n">
         <v>1.3252</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9992</v>
+        <v>-3.2798</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6201</v>
+        <v>-0.1731</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.379</v>
+        <v>-3.1067</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8588</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5329</v>
+        <v>-0.8136</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4675</v>
+        <v>-0.0204</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0654</v>
+        <v>-0.7931</v>
       </c>
       <c r="V24" t="n">
         <v>-2.2599</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3945</v>
+        <v>-4.4761</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2923</v>
+        <v>-4.7335</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1022</v>
+        <v>0.2575</v>
       </c>
       <c r="G25" t="n">
         <v>3.3395</v>
@@ -2404,13 +2404,13 @@
         <v>1.0875</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.4921</v>
+        <v>-1.5736</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.536</v>
+        <v>0.0228</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.9561</v>
+        <v>-1.5965</v>
       </c>
       <c r="V25" t="n">
         <v>-1.6743</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2.020199999999998</v>
+        <v>3.5103</v>
       </c>
       <c r="E26" t="n">
-        <v>15.8593</v>
+        <v>15.8594</v>
       </c>
       <c r="F26" t="n">
-        <v>-13.8391</v>
+        <v>-12.3489</v>
       </c>
       <c r="G26" t="n">
         <v>19.8933</v>
@@ -2482,13 +2482,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.718400000000001</v>
+        <v>-7.2282</v>
       </c>
       <c r="T26" t="n">
-        <v>2.0307</v>
+        <v>2.031</v>
       </c>
       <c r="U26" t="n">
-        <v>-10.7495</v>
+        <v>-9.2592</v>
       </c>
       <c r="V26" t="n">
         <v>-2.6296</v>
